--- a/samples/ss_dkgd_ingest.xlsx
+++ b/samples/ss_dkgd_ingest.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:U17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,57 +536,72 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Bus 150 kV</t>
+          <t>Bus HV</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Bus LV</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Jumlah Trafo</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Kapasitor</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Catatan Simbol</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Sirkit Bay</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Status Operasi</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Status Kerawanan</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>No Kerawanan</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Wilayah</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Sudut Pandang</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Longitude</t>
         </is>
       </c>
     </row>
@@ -623,24 +638,25 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -675,24 +691,25 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -723,42 +740,43 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+          <t>1,3</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
         <is>
           <t>GNDUL</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
         <is>
           <t>2 trafo (IBT 1 &amp; 3)</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -792,33 +810,34 @@
           <t>2</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
         <is>
           <t>DKSBI</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -853,24 +872,25 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -905,24 +925,25 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -957,24 +978,25 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1009,24 +1031,25 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1061,28 +1084,29 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1117,24 +1141,25 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1169,24 +1194,25 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1221,24 +1247,25 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1273,24 +1300,25 @@
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1325,24 +1353,25 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1377,24 +1406,25 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1429,24 +1459,25 @@
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/samples/ss_dkgd_ingest.xlsx
+++ b/samples/ss_dkgd_ingest.xlsx
@@ -870,8 +870,14 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>1 kapasitor 50 MVAr</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
@@ -1192,8 +1198,14 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>1 kapasitor 50 MVAr</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
@@ -1245,8 +1257,14 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>1 kapasitor</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
@@ -1462,7 +1480,7 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Beroperasi</t>
+          <t>Rencana</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
@@ -1490,7 +1508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1702,15 +1720,19 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SKTT Gandul - Kembangan</t>
+          <t>SKTT Durikosambi - Kembangan (bottleneck derating -- kerawanan #1)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>GNDUL</t>
+          <t>DKSBI</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1734,7 +1756,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Sangat Rawan</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -1761,14 +1783,10 @@
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SKTT Durikosambi - Kembangan (bottleneck derating -- kerawanan #1)</t>
+          <t>SKTT Durikosambi - Grogol Baru</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1778,7 +1796,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>KMBGN</t>
+          <t>GRGBR</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1797,7 +1815,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Sangat Rawan</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1827,17 +1845,17 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SKTT Durikosambi - Grogol Baru</t>
+          <t>SUTT Sawangan - Serpong</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DKSBI</t>
+          <t>SWGAN</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GRGBR</t>
+          <t>SRPNG</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1867,10 +1885,10 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -1886,17 +1904,17 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SUTT Sawangan - Serpong</t>
+          <t>SUTT Cirendeu - Petukangan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SWGAN</t>
+          <t>CRNDU</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SRPNG</t>
+          <t>PTKGN</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1945,12 +1963,12 @@
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SUTT Cirendeu - Petukangan</t>
+          <t>SKTT Kembangan - Petukangan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CRNDU</t>
+          <t>KMBGN</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2004,17 +2022,17 @@
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SKTT Kembangan - Petukangan</t>
+          <t>SKTT Grogol Baru - Grogol</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>KMBGN</t>
+          <t>GRGBR</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PTKGN</t>
+          <t>GROGOL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2063,17 +2081,17 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SKTT Grogol Baru - Grogol</t>
+          <t>SUTT Serpong - Bintaro</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>GRGBR</t>
+          <t>SRPNG</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>GROGOL</t>
+          <t>BNTRO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2103,10 +2121,10 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -2122,12 +2140,12 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SUTT Serpong - Bintaro</t>
+          <t>SUTT Petukangan - Bintaro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SRPNG</t>
+          <t>PTKGN</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2181,17 +2199,17 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SUTT Petukangan - Bintaro</t>
+          <t>SKTT Grogol - Tomang</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>PTKGN</t>
+          <t>GROGOL</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BNTRO</t>
+          <t>TMANG</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2240,17 +2258,17 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SKTT Grogol - Tomang</t>
+          <t>SUTT Bintaro - Bintaro Baru (belum energize)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>GROGOL</t>
+          <t>BNTRO</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TMANG</t>
+          <t>BTRBR</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2264,12 +2282,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Beroperasi</t>
+          <t>Rencana</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Rawan</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -2280,10 +2298,10 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -2291,65 +2309,6 @@
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>SUTT Bintaro - Bintaro Baru</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>BNTRO</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>BTRBR</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="n">
-        <v>2</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
-      <c r="N14" t="n">
-        <v>4</v>
-      </c>
-      <c r="O14" t="n">
-        <v>5</v>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Tidak</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/samples/ss_dkgd_ingest.xlsx
+++ b/samples/ss_dkgd_ingest.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U17"/>
+  <dimension ref="A1:U18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -717,7 +717,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IBT 1,3 Gandul</t>
+          <t>IBT 1 Gandul</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1,3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -750,14 +750,10 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>2 trafo (IBT 1 &amp; 3)</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
@@ -784,12 +780,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IBT 2 Durikosambi</t>
+          <t>IBT 3 Gandul</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>IBT 2 DKSBI</t>
+          <t>IBT 3 GNDUL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -807,16 +803,18 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>DKSBI</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>GNDUL</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
@@ -845,39 +843,41 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Gandul (bus 150 kV)</t>
+          <t>IBT 2 Durikosambi</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GNDUL</t>
+          <t>IBT 2 DKSBI</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>DKSBI</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>1 kapasitor 50 MVAr</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
@@ -904,12 +904,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Durikosambi (bus 150 kV)</t>
+          <t>Gandul (bus 150 kV)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DKSBI</t>
+          <t>GNDUL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -929,8 +929,14 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>1 kapasitor 50 MVAr</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
@@ -957,12 +963,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sawangan</t>
+          <t>Durikosambi (bus 150 kV)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SWGAN</t>
+          <t>DKSBI</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -971,7 +977,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1010,12 +1016,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cirendeu</t>
+          <t>Sawangan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CRNDU</t>
+          <t>SWGAN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1063,12 +1069,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kembangan</t>
+          <t>Cirendeu</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>KMBGN</t>
+          <t>CRNDU</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1099,14 +1105,10 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
@@ -1120,17 +1122,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Grogol Baru</t>
+          <t>Kembangan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GRGBR</t>
+          <t>KMBGN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Busbar GIS</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1156,10 +1158,14 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="R11" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
@@ -1173,21 +1179,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Serpong</t>
+          <t>Grogol Baru</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SRPNG</t>
+          <t>GRGBR</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Busbar GIS</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1198,14 +1204,8 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>1 kapasitor 50 MVAr</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Petukangan</t>
+          <t>Serpong</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PTKGN</t>
+          <t>SRPNG</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1 kapasitor</t>
+          <t>1 kapasitor 50 MVAr</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -1291,17 +1291,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Grogol</t>
+          <t>Petukangan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GROGOL</t>
+          <t>PTKGN</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Busbar GIS</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1316,8 +1316,14 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1 kapasitor</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
@@ -1344,21 +1350,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bintaro</t>
+          <t>Grogol</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BNTRO</t>
+          <t>GROGOL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Busbar GIS</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1397,17 +1403,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tomang</t>
+          <t>Bintaro</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TMANG</t>
+          <t>BNTRO</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Busbar GIS</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1450,21 +1456,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bintaro Baru</t>
+          <t>Tomang</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BTRBR</t>
+          <t>TMANG</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Busbar GIS</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1480,7 +1486,7 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Rencana</t>
+          <t>Beroperasi</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
@@ -1496,6 +1502,59 @@
         </is>
       </c>
       <c r="S17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Bintaro Baru</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BTRBR</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2258,7 +2317,7 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SUTT Bintaro - Bintaro Baru (belum energize)</t>
+          <t>SKTT Bintaro - Bintaro Baru</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2282,12 +2341,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Rencana</t>
+          <t>Beroperasi</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Rawan</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -2321,7 +2380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2347,25 +2406,30 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Jenis</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Tegangan</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Sirkit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Status Operasi</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>No Kerawanan</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Sudut Pandang</t>
         </is>
@@ -2390,21 +2454,22 @@
           <t>SRPNG</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
         <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2425,21 +2490,22 @@
           <t>PTKGN</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
         <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>1</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
